--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -393,10 +393,10 @@
         <v>2023</v>
       </c>
       <c r="C2">
+        <v>26.52789911810764</v>
+      </c>
+      <c r="D2">
         <v>37.35555921865985</v>
-      </c>
-      <c r="D2">
-        <v>26.52789911810764</v>
       </c>
       <c r="E2">
         <v>2.676977726786325</v>
@@ -454,16 +454,16 @@
         <v>2018</v>
       </c>
       <c r="B2">
+        <v>30.96463348286845</v>
+      </c>
+      <c r="C2">
+        <v>28.31591931816716</v>
+      </c>
+      <c r="D2">
         <v>26.09399171923384</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>30.40542921858278</v>
-      </c>
-      <c r="D2">
-        <v>30.96463348286845</v>
-      </c>
-      <c r="E2">
-        <v>28.31591931816716</v>
       </c>
       <c r="F2">
         <v>3.832299828864059</v>
@@ -477,16 +477,16 @@
         <v>2019</v>
       </c>
       <c r="B3">
+        <v>30.71165626375393</v>
+      </c>
+      <c r="C3">
+        <v>27.24840616867387</v>
+      </c>
+      <c r="D3">
         <v>26.98100995207131</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>31.41581955299838</v>
-      </c>
-      <c r="D3">
-        <v>30.71165626375393</v>
-      </c>
-      <c r="E3">
-        <v>27.24840616867387</v>
       </c>
       <c r="F3">
         <v>3.706310481988576</v>
@@ -500,16 +500,16 @@
         <v>2020</v>
       </c>
       <c r="B4">
+        <v>29.29313247284859</v>
+      </c>
+      <c r="C4">
+        <v>26.13866016686466</v>
+      </c>
+      <c r="D4">
         <v>28.337590420799</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>33.18509073778215</v>
-      </c>
-      <c r="D4">
-        <v>29.29313247284859</v>
-      </c>
-      <c r="E4">
-        <v>26.13866016686466</v>
       </c>
       <c r="F4">
         <v>3.528881549738357</v>
@@ -523,16 +523,16 @@
         <v>2021</v>
       </c>
       <c r="B5">
+        <v>28.1958714984216</v>
+      </c>
+      <c r="C5">
+        <v>25.90358739357998</v>
+      </c>
+      <c r="D5">
         <v>30.43836759383663</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>35.91462898356894</v>
-      </c>
-      <c r="D5">
-        <v>28.1958714984216</v>
-      </c>
-      <c r="E5">
-        <v>25.90358739357998</v>
       </c>
       <c r="F5">
         <v>3.285327299229039</v>
@@ -546,16 +546,16 @@
         <v>2022</v>
       </c>
       <c r="B6">
+        <v>27.7896259030398</v>
+      </c>
+      <c r="C6">
+        <v>27.13511160688426</v>
+      </c>
+      <c r="D6">
         <v>30.85942857605788</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>36.24703956677959</v>
-      </c>
-      <c r="D6">
-        <v>27.7896259030398</v>
-      </c>
-      <c r="E6">
-        <v>27.13511160688426</v>
       </c>
       <c r="F6">
         <v>3.240500703165465</v>
@@ -569,16 +569,16 @@
         <v>2023</v>
       </c>
       <c r="B7">
+        <v>27.41672147958797</v>
+      </c>
+      <c r="C7">
+        <v>26.52789911810764</v>
+      </c>
+      <c r="D7">
         <v>32.03512600577511</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>37.35555921865985</v>
-      </c>
-      <c r="D7">
-        <v>27.41672147958797</v>
-      </c>
-      <c r="E7">
-        <v>26.52789911810764</v>
       </c>
       <c r="F7">
         <v>3.121573487239369</v>
@@ -592,16 +592,16 @@
         <v>2024</v>
       </c>
       <c r="B8">
+        <v>26.56912786797274</v>
+      </c>
+      <c r="C8">
+        <v>25.52741152550883</v>
+      </c>
+      <c r="D8">
         <v>33.29424476531351</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>38.85412176256943</v>
-      </c>
-      <c r="D8">
-        <v>26.56912786797274</v>
-      </c>
-      <c r="E8">
-        <v>25.52741152550883</v>
       </c>
       <c r="F8">
         <v>3.003522101338716</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.96658295528192</v>
+      </c>
+      <c r="C2">
         <v>38.26211114711601</v>
-      </c>
-      <c r="C2">
-        <v>24.96658295528192</v>
       </c>
       <c r="D2">
         <v>2.613551552749004</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.01876205505874</v>
+      </c>
+      <c r="C3">
         <v>19.44590566368578</v>
-      </c>
-      <c r="C3">
-        <v>31.01876205505874</v>
       </c>
       <c r="D3">
         <v>5.142470694319207</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.32632959503225</v>
+      </c>
+      <c r="C4">
         <v>33.82537940633281</v>
-      </c>
-      <c r="C4">
-        <v>28.32632959503225</v>
       </c>
       <c r="D4">
         <v>2.956360039564788</v>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.5215094606293</v>
+      </c>
+      <c r="C5">
         <v>38.59159408511916</v>
-      </c>
-      <c r="C5">
-        <v>27.5215094606293</v>
       </c>
       <c r="D5">
         <v>2.591237868522249</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.70830705184811</v>
+      </c>
+      <c r="C6">
         <v>34.0552857323073</v>
-      </c>
-      <c r="C6">
-        <v>27.70830705184811</v>
       </c>
       <c r="D6">
         <v>2.936401731762091</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.98451872004146</v>
+      </c>
+      <c r="C7">
         <v>42.06260525974867</v>
-      </c>
-      <c r="C7">
-        <v>27.98451872004146</v>
       </c>
       <c r="D7">
         <v>2.377408612292826</v>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.5470415493888</v>
+      </c>
+      <c r="C8">
         <v>32.17562720372308</v>
-      </c>
-      <c r="C8">
-        <v>28.5470415493888</v>
       </c>
       <c r="D8">
         <v>3.1079425232907</v>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="B9">
+        <v>26.64065741798317</v>
+      </c>
+      <c r="C9">
         <v>38.19124497888888</v>
-      </c>
-      <c r="C9">
-        <v>26.64065741798317</v>
       </c>
       <c r="D9">
         <v>2.618401155952821</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:05</t>
+    <t xml:space="preserve">2026-07-30 18:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -59,16 +59,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_d_otrasrel_a_2023_valparaiso.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Otras relaciones demograficas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Valparaiso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
   <si>
     <t xml:space="preserve">year</t>
@@ -575,23 +584,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -616,25 +625,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -818,7 +827,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -832,7 +841,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>24.97</v>
@@ -846,7 +855,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>31.02</v>
@@ -860,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>28.33</v>
@@ -874,7 +883,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>27.52</v>
@@ -888,7 +897,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>27.71</v>
@@ -902,7 +911,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>27.98</v>
@@ -916,7 +925,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>28.55</v>
@@ -930,7 +939,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>26.64</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 18:30</t>
+    <t xml:space="preserve">2026-08-07 07:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:07</t>
+    <t xml:space="preserve">2026-08-17 16:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:36</t>
+    <t xml:space="preserve">2026-08-19 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:11</t>
+    <t xml:space="preserve">2026-08-28 11:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:06</t>
+    <t xml:space="preserve">2026-09-04 20:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2023_valparaiso.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:39</t>
+    <t xml:space="preserve">2026-09-06 17:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
